--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129688615</v>
+        <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>91117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647283</v>
+        <v>647314</v>
       </c>
       <c r="R2" t="n">
-        <v>7235926</v>
+        <v>7235743</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -784,6 +794,238 @@
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137007616</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137007663</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93423</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Holmfors, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>647267</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7235771</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137007663</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129688615</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Holmfors, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>647283</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7235926</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129688615</t>
         </is>
@@ -792,6 +1034,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40661-2026 artfynd.xlsx
+++ b/artfynd/A 40661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137007616</v>
       </c>
       <c r="B2" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137007663</v>
       </c>
       <c r="B3" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
